--- a/data/wf_template.xlsx
+++ b/data/wf_template.xlsx
@@ -8,12 +8,22 @@
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
-    <sheet name="production" sheetId="2" r:id="rId2"/>
-    <sheet name="hierarchy" sheetId="3" r:id="rId3"/>
-    <sheet name="stooip" sheetId="4" r:id="rId4"/>
+    <sheet name="wells" sheetId="2" r:id="rId2"/>
+    <sheet name="alloc" sheetId="3" r:id="rId3"/>
+    <sheet name="vol" sheetId="4" r:id="rId4"/>
     <sheet name="fluids" sheetId="5" r:id="rId5"/>
-    <sheet name="petrophysics" sheetId="6" r:id="rId6"/>
-    <sheet name="allocation" sheetId="7" r:id="rId7"/>
+    <sheet name="injsand" sheetId="6" r:id="rId6"/>
+    <sheet name="injsand_status" sheetId="7" r:id="rId7"/>
+    <sheet name="hierarchy" sheetId="8" r:id="rId8"/>
+    <sheet name="baseline" sheetId="9" r:id="rId9"/>
+    <sheet name="prototypes" sheetId="10" r:id="rId10"/>
+    <sheet name="prototype_assign" sheetId="11" r:id="rId11"/>
+    <sheet name="interventions" sheetId="12" r:id="rId12"/>
+    <sheet name="well_status" sheetId="13" r:id="rId13"/>
+    <sheet name="patterns" sheetId="14" r:id="rId14"/>
+    <sheet name="patterns_vel" sheetId="15" r:id="rId15"/>
+    <sheet name="patterns_mat" sheetId="16" r:id="rId16"/>
+    <sheet name="injsand_calc" sheetId="17" r:id="rId17"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -357,7 +367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -368,25 +378,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>column</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>accepted_aliases</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -395,38 +410,48 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>wells</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>well</t>
         </is>
       </c>
-      <c r="C2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>well_name, pozo, uwi, wellname</t>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>well_name, pozo, uwi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>wells</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>date</t>
         </is>
       </c>
-      <c r="C3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>month, fecha, period, mes</t>
         </is>
@@ -435,460 +460,525 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>wells</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>bopd</t>
         </is>
       </c>
-      <c r="C4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>stb/d</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>oil_rate, qo, oil_bpd</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oil rate</t>
+          <t>oil_rate, qo</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>wells</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>bwpd</t>
         </is>
       </c>
-      <c r="C5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>stb/d</t>
-        </is>
+      <c r="D5" t="b">
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>water_rate, qw, water_bpd</t>
+          <t>bbl/d</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Water production rate</t>
+          <t>water_rate, qw</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>wells</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>bwipd</t>
         </is>
       </c>
-      <c r="C6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>stb/d</t>
-        </is>
+      <c r="D6" t="b">
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>winj, water_inj, qwi, inj_rate, bwpid</t>
+          <t>bbl/d</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Water injection rate</t>
+          <t>winj, qwi, inj_rate</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hierarchy</t>
+          <t>alloc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>field</t>
-        </is>
-      </c>
-      <c r="C7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>campo</t>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>well_name, pozo, uwi</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hierarchy</t>
+          <t>alloc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>block</t>
-        </is>
-      </c>
-      <c r="C8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>sector, area, bloque, segment</t>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>patron, pattern_name</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hierarchy</t>
+          <t>alloc</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="C9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>patron, pattern_name, pattern_id</t>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>valid_from, fecha, month, effective_date</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hierarchy</t>
+          <t>alloc</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>well</t>
-        </is>
-      </c>
-      <c r="C10" t="b">
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>coeff</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>well_name, pozo, uwi</t>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>coefficient, coef, factor, af</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hierarchy</t>
+          <t>vol</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>well_type</t>
-        </is>
-      </c>
-      <c r="C11" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>type, tipo, role</t>
-        </is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PRODUCER or INJECTOR</t>
+          <t>patron</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hierarchy</t>
+          <t>vol</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>m / ft</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>x_coord, easting, coord_x</t>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>reservoir</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>yacimiento, formation</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hierarchy</t>
+          <t>vol</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="C13" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>m / ft</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>y_coord, northing, coord_y</t>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>sand</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>unit, unidad, arena, layer, zone</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>stooip</t>
+          <t>vol</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="C14" t="b">
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>stoiip</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>patron, pattern_name</t>
+          <t>stb</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>stooip, ooip, poes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>stooip</t>
+          <t>vol</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sand</t>
-        </is>
-      </c>
-      <c r="C15" t="b">
-        <v>1</v>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>hcpv</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>sand_index, sandindex, sandxind, zone, unit, arena, layer</t>
+          <t>rb</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>hcpv_rb, vph</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>stooip</t>
+          <t>vol</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>stooip</t>
-        </is>
-      </c>
-      <c r="C16" t="b">
-        <v>1</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>stb</t>
-        </is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>stooip_stb, ooip, poes, n</t>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>net_pay, hn, thickness</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>stooip</t>
+          <t>vol</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>area</t>
-        </is>
-      </c>
-      <c r="C17" t="b">
-        <v>0</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>acres</t>
-        </is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>phi</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>area_acres</t>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>porosity, por</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>stooip</t>
+          <t>vol</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>net_pay</t>
-        </is>
-      </c>
-      <c r="C18" t="b">
-        <v>0</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ft</t>
-        </is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>h, net_pay_ft, hn, thickness</t>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>swi, sw_init</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>stooip</t>
+          <t>vol</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>porosity</t>
-        </is>
-      </c>
-      <c r="C19" t="b">
-        <v>0</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>frac</t>
-        </is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>phi, por</t>
+          <t>mD</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>perm, permeability, k_md</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>stooip</t>
+          <t>fluids</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>swi</t>
-        </is>
-      </c>
-      <c r="C20" t="b">
-        <v>0</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>frac</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>sw, sw_init, swo</t>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>reservoir</t>
+        </is>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>yacimiento, sand, region</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>stooip</t>
+          <t>fluids</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>permeability</t>
-        </is>
-      </c>
-      <c r="C21" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>mD</t>
-        </is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>k, perm, k_md</t>
+          <t>API</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>stooip</t>
+          <t>fluids</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>boi</t>
-        </is>
-      </c>
-      <c r="C22" t="b">
-        <v>0</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>rb/stb</t>
-        </is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>rs</t>
+        </is>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>bo_i, bo_init</t>
+          <t>scf/stb</t>
         </is>
       </c>
     </row>
@@ -900,15 +990,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sand</t>
-        </is>
-      </c>
-      <c r="C23" t="b">
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>bo</t>
+        </is>
+      </c>
+      <c r="D23" t="b">
         <v>1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>sand_index, zone, unit, arena, layer, region</t>
+          <t>rb/stb</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>bo_rb_stb</t>
         </is>
       </c>
     </row>
@@ -920,20 +1020,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>bo</t>
-        </is>
-      </c>
-      <c r="C24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D24" t="inlineStr">
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>bw</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>rb/stb</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>bo_rb_stb</t>
         </is>
       </c>
     </row>
@@ -945,20 +1045,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>bw</t>
-        </is>
-      </c>
-      <c r="C25" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>rb/stb</t>
-        </is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>visco</t>
+        </is>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>bw_rb_stb</t>
+          <t>cp</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>mu_o, muo</t>
         </is>
       </c>
     </row>
@@ -970,20 +1075,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>mu_o</t>
-        </is>
-      </c>
-      <c r="C26" t="b">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr">
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>viscw</t>
+        </is>
+      </c>
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>cp</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>muo, visc_oil, uo</t>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>mu_w, muw</t>
         </is>
       </c>
     </row>
@@ -995,20 +1105,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>mu_w</t>
-        </is>
-      </c>
-      <c r="C27" t="b">
-        <v>0</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>cp</t>
-        </is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>swc</t>
+        </is>
+      </c>
+      <c r="D27" t="b">
+        <v>0</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>muw, visc_water, uw</t>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>swir</t>
         </is>
       </c>
     </row>
@@ -1020,20 +1135,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>swc</t>
-        </is>
-      </c>
-      <c r="C28" t="b">
-        <v>1</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>frac</t>
-        </is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>sor</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>swir, swcr</t>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>sorw</t>
         </is>
       </c>
     </row>
@@ -1045,20 +1165,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sor</t>
-        </is>
-      </c>
-      <c r="C29" t="b">
-        <v>1</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>frac</t>
-        </is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>krw</t>
+        </is>
+      </c>
+      <c r="D29" t="b">
+        <v>0</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>sorw</t>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>krw_or, krw_max</t>
         </is>
       </c>
     </row>
@@ -1070,25 +1195,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>krw_or</t>
-        </is>
-      </c>
-      <c r="C30" t="b">
-        <v>0</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>frac</t>
-        </is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>kro</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>krw_max, krw_end, krwor</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>krw at Sor</t>
+          <t>kro_wc, kro_max</t>
         </is>
       </c>
     </row>
@@ -1100,25 +1225,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>kro_wc</t>
-        </is>
-      </c>
-      <c r="C31" t="b">
-        <v>0</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>frac</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>kro_max, kro_end, krowc</t>
-        </is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>nw</t>
+        </is>
+      </c>
+      <c r="D31" t="b">
+        <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>kro at Swc</t>
+          <t>corey_w</t>
         </is>
       </c>
     </row>
@@ -1130,270 +1250,1856 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nw</t>
-        </is>
-      </c>
-      <c r="C32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>corey_w, n_w</t>
-        </is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D32" t="b">
+        <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Corey exponent, water</t>
+          <t>corey_o</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>fluids</t>
+          <t>injsand</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="b">
-        <v>0</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>corey_o, n_o</t>
-        </is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="D33" t="b">
+        <v>1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Corey exponent, oil</t>
+          <t>pozo</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>petrophysics</t>
+          <t>injsand</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>well</t>
-        </is>
-      </c>
-      <c r="C34" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>well_name, pozo, uwi</t>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>sand</t>
+        </is>
+      </c>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>unit, unidad, arena</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>petrophysics</t>
+          <t>injsand</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>sand</t>
-        </is>
-      </c>
-      <c r="C35" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>sand_index, zone, unit, arena, layer</t>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>fecha, month</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>petrophysics</t>
+          <t>injsand</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>net_pay</t>
-        </is>
-      </c>
-      <c r="C36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>ft</t>
-        </is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>bwipd</t>
+        </is>
+      </c>
+      <c r="D36" t="b">
+        <v>1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>h, net_pay_ft, hn, thickness</t>
+          <t>bbl/d</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>winj, rate, qwi</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>petrophysics</t>
+          <t>injsand_status</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>porosity</t>
-        </is>
-      </c>
-      <c r="C37" t="b">
-        <v>0</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>frac</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>phi, por</t>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>pozo</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>petrophysics</t>
+          <t>injsand_status</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>sw</t>
-        </is>
-      </c>
-      <c r="C38" t="b">
-        <v>0</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>frac</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>swi</t>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>sand</t>
+        </is>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>unit, unidad, arena</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>petrophysics</t>
+          <t>injsand_status</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>permeability</t>
-        </is>
-      </c>
-      <c r="C39" t="b">
-        <v>0</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>mD</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>k, perm, k_md</t>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D39" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>fecha</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>allocation</t>
+          <t>injsand_status</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="C40" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>patron, pattern_name</t>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>vrf</t>
+        </is>
+      </c>
+      <c r="D40" t="b">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>valve, valvula, valve_size</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>allocation</t>
+          <t>injsand_status</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>well</t>
-        </is>
-      </c>
-      <c r="C41" t="b">
-        <v>1</v>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>cobb</t>
+        </is>
+      </c>
+      <c r="D41" t="b">
+        <v>0</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>well_name, pozo, uwi</t>
+          <t>bbl/d</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>design_rate, optimum_rate, caudal_optimo</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>allocation</t>
+          <t>hierarchy</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>coefficient</t>
-        </is>
-      </c>
-      <c r="C42" t="b">
-        <v>1</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>frac</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>coef, factor, alloc, allocation, fraction, af</t>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D42" t="b">
+        <v>0</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>campo</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>allocation</t>
+          <t>hierarchy</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="D43" t="b">
+        <v>0</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>block, sector, bloque</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>hierarchy</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>patron</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>hierarchy</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="D45" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>pozo</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>hierarchy</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>well_type</t>
+        </is>
+      </c>
+      <c r="D46" t="b">
+        <v>0</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>type, tipo, role</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>hierarchy</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D47" t="b">
+        <v>0</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>x_coord, easting</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>hierarchy</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="D48" t="b">
+        <v>0</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>y_coord, northing</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D49" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>patron</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>wf_start</t>
+        </is>
+      </c>
+      <c r="D50" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>start, fecha_inicio, waterflood_start</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>np_primary</t>
+        </is>
+      </c>
+      <c r="D51" t="b">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>stb</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>np_base, primary_np</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>prototypes</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>prototype</t>
+        </is>
+      </c>
+      <c r="D52" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>name, prototipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>prototypes</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="D53" t="b">
+        <v>0</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>prototypes</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>dwi</t>
+        </is>
+      </c>
+      <c r="D54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>prototypes</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>sec_rf</t>
+        </is>
+      </c>
+      <c r="D55" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>secrf, rf</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>prototypes</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>dwp</t>
+        </is>
+      </c>
+      <c r="D56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>prototypes</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>util</t>
+        </is>
+      </c>
+      <c r="D57" t="b">
+        <v>0</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>utilization</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>prototypes</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>wor</t>
+        </is>
+      </c>
+      <c r="D58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>prototype_assign</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D59" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>patron</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>prototype_assign</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>prototype</t>
+        </is>
+      </c>
+      <c r="D60" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>prototipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>prototype_assign</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="D61" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>prototype_assign</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>valid_from</t>
+        </is>
+      </c>
+      <c r="D62" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>date, fecha</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>interventions</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="D63" t="b">
+        <v>1</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>pozo</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>interventions</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>date</t>
         </is>
       </c>
-      <c r="C43" t="b">
-        <v>0</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>month, fecha, effective_date, from</t>
+      <c r="D64" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>interventions</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D65" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>job, tipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>interventions</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>sand</t>
+        </is>
+      </c>
+      <c r="D66" t="b">
+        <v>0</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>unit, arena</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>interventions</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D67" t="b">
+        <v>0</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>interventions</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D68" t="b">
+        <v>0</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>comment, comentario</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>well_status</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="D69" t="b">
+        <v>1</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>pozo</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>well_status</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D70" t="b">
+        <v>1</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>well_status</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D71" t="b">
+        <v>0</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>well_status</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>lift</t>
+        </is>
+      </c>
+      <c r="D72" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>lift_type, sla</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>well_status</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>dfl</t>
+        </is>
+      </c>
+      <c r="D73" t="b">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>fluid_level, nivel, submergence</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>patterns</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>patterns</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>patterns</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>bopd</t>
+        </is>
+      </c>
+      <c r="D76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>patterns</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>bwpd</t>
+        </is>
+      </c>
+      <c r="D77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>patterns</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>bwipd</t>
+        </is>
+      </c>
+      <c r="D78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>patterns_vel</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D79" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>patterns_vel</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>patterns_vel</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>wor</t>
+        </is>
+      </c>
+      <c r="D81" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>patterns_vel</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>util</t>
+        </is>
+      </c>
+      <c r="D82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>patterns_vel</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="D83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>patterns_vel</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>iwr</t>
+        </is>
+      </c>
+      <c r="D84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D85" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>np</t>
+        </is>
+      </c>
+      <c r="D87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>nw</t>
+        </is>
+      </c>
+      <c r="D88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>nwi</t>
+        </is>
+      </c>
+      <c r="D89" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>iwrcum</t>
+        </is>
+      </c>
+      <c r="D90" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>opr</t>
+        </is>
+      </c>
+      <c r="D91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>wpr</t>
+        </is>
+      </c>
+      <c r="D92" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>injsand_calc</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>injsand_calc</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>sand</t>
+        </is>
+      </c>
+      <c r="D94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>injsand_calc</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>injsand_calc</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="D96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>injsand_calc</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>nwi</t>
+        </is>
+      </c>
+      <c r="D97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>prototype</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>dwi</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sec_rf</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>dwp</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>util</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>wor</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>prototype</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>valid_from</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sand</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>lift</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>dfl</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>bopd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>bwpd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>bwipd</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>wor</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>util</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>iwr</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>np</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nw</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>nwi</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>iwrcum</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>opr</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>wpr</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sand</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>nwi</t>
         </is>
       </c>
     </row>
@@ -1441,43 +3147,28 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>field</t>
+          <t>well</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>well</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>well_type</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>y</t>
+          <t>coeff</t>
         </is>
       </c>
     </row>
@@ -1499,42 +3190,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>reservoir</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>sand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>stooip</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>stoiip</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>net_pay</t>
+          <t>hcpv</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>porosity</t>
+          <t>h</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>swi</t>
+          <t>phi</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>permeability</t>
+          <t>sw</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>boi</t>
+          <t>k</t>
         </is>
       </c>
     </row>
@@ -1545,61 +3236,71 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>sand</t>
+          <t>reservoir</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>rs</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>bo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>bw</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>mu_o</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu_w</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>visco</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>viscw</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>swc</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>sor</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>krw_or</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>kro_wc</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>krw</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>kro</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>nw</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1612,7 +3313,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1628,22 +3329,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>net_pay</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>porosity</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>sw</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>permeability</t>
+          <t>bwipd</t>
         </is>
       </c>
     </row>
@@ -1654,28 +3345,107 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sand</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>vrf</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>cobb</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>pattern</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>well_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>well</t>
+          <t>wf_start</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>coefficient</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
+          <t>np_primary</t>
         </is>
       </c>
     </row>

--- a/data/wf_template.xlsx
+++ b/data/wf_template.xlsx
@@ -20,10 +20,13 @@
     <sheet name="prototype_assign" sheetId="11" r:id="rId11"/>
     <sheet name="interventions" sheetId="12" r:id="rId12"/>
     <sheet name="well_status" sheetId="13" r:id="rId13"/>
-    <sheet name="patterns" sheetId="14" r:id="rId14"/>
-    <sheet name="patterns_vel" sheetId="15" r:id="rId15"/>
-    <sheet name="patterns_mat" sheetId="16" r:id="rId16"/>
-    <sheet name="injsand_calc" sheetId="17" r:id="rId17"/>
+    <sheet name="intervals" sheetId="14" r:id="rId14"/>
+    <sheet name="profiles" sheetId="15" r:id="rId15"/>
+    <sheet name="findings" sheetId="16" r:id="rId16"/>
+    <sheet name="patterns" sheetId="17" r:id="rId17"/>
+    <sheet name="patterns_vel" sheetId="18" r:id="rId18"/>
+    <sheet name="patterns_mat" sheetId="19" r:id="rId19"/>
+    <sheet name="injsand_calc" sheetId="20" r:id="rId20"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -367,7 +370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1515,7 +1518,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>field</t>
+          <t>orgunit</t>
         </is>
       </c>
       <c r="D42" t="b">
@@ -1523,7 +1526,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>campo</t>
+          <t>org_unit, unidad_organizacional, business_unit, asset</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1543,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="D43" t="b">
@@ -1548,7 +1551,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>block, sector, bloque</t>
+          <t>contrato, block_contract</t>
         </is>
       </c>
     </row>
@@ -1565,15 +1568,15 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>field</t>
         </is>
       </c>
       <c r="D44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>patron</t>
+          <t>campo</t>
         </is>
       </c>
     </row>
@@ -1590,15 +1593,15 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>well</t>
+          <t>structure</t>
         </is>
       </c>
       <c r="D45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>pozo</t>
+          <t>estructura</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1618,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>well_type</t>
+          <t>substructure</t>
         </is>
       </c>
       <c r="D46" t="b">
@@ -1623,7 +1626,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>type, tipo, role</t>
+          <t>subestructura, sub_structure</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1643,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>area</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -1648,7 +1651,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>x_coord, easting</t>
+          <t>block, sector, bloque</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1668,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D48" t="b">
@@ -1673,14 +1676,14 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>y_coord, northing</t>
+          <t>patron</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>hierarchy</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1690,7 +1693,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>well</t>
         </is>
       </c>
       <c r="D49" t="b">
@@ -1698,14 +1701,14 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>patron</t>
+          <t>pozo</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>hierarchy</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1715,22 +1718,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>wf_start</t>
+          <t>well_type</t>
         </is>
       </c>
       <c r="D50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>start, fecha_inicio, waterflood_start</t>
+          <t>type, tipo, role</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>hierarchy</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1740,136 +1743,146 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>np_primary</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D51" t="b">
         <v>0</v>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>stb</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>np_base, primary_np</t>
+          <t>x_coord, easting</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>prototypes</t>
+          <t>hierarchy</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>prototype</t>
+          <t>y</t>
         </is>
       </c>
       <c r="D52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>name, prototipo</t>
+          <t>y_coord, northing</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>prototypes</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ver</t>
+          <t>patron</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>prototypes</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>dwi</t>
+          <t>wf_start</t>
         </is>
       </c>
       <c r="D54" t="b">
         <v>1</v>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>start, fecha_inicio, waterflood_start</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>prototypes</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>sec_rf</t>
+          <t>np_primary</t>
         </is>
       </c>
       <c r="D55" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>stb</t>
+        </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>secrf, rf</t>
+          <t>np_base, primary_np</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>prototypes</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>dwp</t>
+          <t>method</t>
         </is>
       </c>
       <c r="D56" t="b">
         <v>0</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>mechanism, metodo, process, drive</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -1885,15 +1898,15 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>util</t>
+          <t>prototype</t>
         </is>
       </c>
       <c r="D57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>utilization</t>
+          <t>name, prototipo</t>
         </is>
       </c>
     </row>
@@ -1910,17 +1923,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>wor</t>
+          <t>version</t>
         </is>
       </c>
       <c r="D58" t="b">
         <v>0</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>prototype_assign</t>
+          <t>prototypes</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1930,22 +1948,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>dwi</t>
         </is>
       </c>
       <c r="D59" t="b">
         <v>1</v>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>patron</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>prototype_assign</t>
+          <t>prototypes</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1955,7 +1968,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>prototype</t>
+          <t>sec_rf</t>
         </is>
       </c>
       <c r="D60" t="b">
@@ -1963,14 +1976,14 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>prototipo</t>
+          <t>secrf, rf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>prototype_assign</t>
+          <t>prototypes</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1980,22 +1993,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>dwp</t>
         </is>
       </c>
       <c r="D61" t="b">
         <v>0</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>prototype_assign</t>
+          <t>prototypes</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2005,7 +2013,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>valid_from</t>
+          <t>util</t>
         </is>
       </c>
       <c r="D62" t="b">
@@ -2013,49 +2021,44 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>date, fecha</t>
+          <t>utilization</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>interventions</t>
+          <t>prototypes</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>well</t>
+          <t>wor</t>
         </is>
       </c>
       <c r="D63" t="b">
-        <v>1</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>pozo</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>interventions</t>
+          <t>prototype_assign</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D64" t="b">
@@ -2063,24 +2066,24 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>fecha</t>
+          <t>patron</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>interventions</t>
+          <t>prototype_assign</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>prototype</t>
         </is>
       </c>
       <c r="D65" t="b">
@@ -2088,24 +2091,24 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>job, tipo</t>
+          <t>prototipo</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>interventions</t>
+          <t>prototype_assign</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>sand</t>
+          <t>version</t>
         </is>
       </c>
       <c r="D66" t="b">
@@ -2113,24 +2116,24 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>unit, arena</t>
+          <t>ver</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>interventions</t>
+          <t>prototype_assign</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>valid_from</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -2138,7 +2141,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>estado</t>
+          <t>date, fecha</t>
         </is>
       </c>
     </row>
@@ -2155,22 +2158,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>well</t>
         </is>
       </c>
       <c r="D68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>comment, comentario</t>
+          <t>pozo</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>well_status</t>
+          <t>interventions</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2180,7 +2183,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>well</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -2188,14 +2191,14 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>pozo</t>
+          <t>fecha</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>well_status</t>
+          <t>interventions</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2205,7 +2208,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>type</t>
         </is>
       </c>
       <c r="D70" t="b">
@@ -2213,14 +2216,14 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>fecha</t>
+          <t>job, tipo</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>well_status</t>
+          <t>interventions</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2230,7 +2233,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>sand</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -2238,14 +2241,14 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>estado</t>
+          <t>unit, arena</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>well_status</t>
+          <t>interventions</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2255,7 +2258,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>lift</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D72" t="b">
@@ -2263,14 +2266,14 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>lift_type, sla</t>
+          <t>estado</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>well_status</t>
+          <t>interventions</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2280,52 +2283,52 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>dfl</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D73" t="b">
         <v>0</v>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>ft</t>
-        </is>
-      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>fluid_level, nivel, submergence</t>
+          <t>comment, comentario</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>patterns</t>
+          <t>well_status</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>well</t>
         </is>
       </c>
       <c r="D74" t="b">
         <v>1</v>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>pozo</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>patterns</t>
+          <t>well_status</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2336,444 +2339,1994 @@
       <c r="D75" t="b">
         <v>1</v>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>patterns</t>
+          <t>well_status</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>bopd</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D76" t="b">
         <v>0</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>estado</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>patterns</t>
+          <t>well_status</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>bwpd</t>
+          <t>lift</t>
         </is>
       </c>
       <c r="D77" t="b">
         <v>0</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>lift_type, sla</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>patterns</t>
+          <t>well_status</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>bwipd</t>
+          <t>dfl</t>
         </is>
       </c>
       <c r="D78" t="b">
         <v>0</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>fluid_level, nivel, submergence</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>patterns_vel</t>
+          <t>intervals</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>orgunit</t>
         </is>
       </c>
       <c r="D79" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>org_unit</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>patterns_vel</t>
+          <t>intervals</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>field</t>
         </is>
       </c>
       <c r="D80" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>patterns_vel</t>
+          <t>intervals</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>wor</t>
+          <t>well</t>
         </is>
       </c>
       <c r="D81" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>pozo</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>patterns_vel</t>
+          <t>intervals</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>util</t>
+          <t>sand</t>
         </is>
       </c>
       <c r="D82" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>unit, unidad, arena</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>patterns_vel</t>
+          <t>intervals</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>tp</t>
+          <t>interval_id</t>
         </is>
       </c>
       <c r="D83" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>intervalo_id, intervalo, interval</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>patterns_vel</t>
+          <t>intervals</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>iwr</t>
+          <t>top_ft</t>
         </is>
       </c>
       <c r="D84" t="b">
         <v>0</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>top, tope</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>patterns_mat</t>
+          <t>intervals</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>base_ft</t>
         </is>
       </c>
       <c r="D85" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>base, bottom</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>patterns_mat</t>
+          <t>intervals</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>estado</t>
         </is>
       </c>
       <c r="D86" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>estado_apertura, status, opening_status</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>patterns_mat</t>
+          <t>intervals</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>h_net_ft</t>
         </is>
       </c>
       <c r="D87" t="b">
         <v>0</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>h_net, hnet, net_pay</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>patterns_mat</t>
+          <t>intervals</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>nw</t>
+          <t>kabs_md</t>
         </is>
       </c>
       <c r="D88" t="b">
         <v>0</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>mD</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>kabs, k_md, k</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>patterns_mat</t>
+          <t>intervals</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>nwi</t>
+          <t>phi</t>
         </is>
       </c>
       <c r="D89" t="b">
         <v>0</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>porosity</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>patterns_mat</t>
+          <t>intervals</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>iwrcum</t>
+          <t>sw_las</t>
         </is>
       </c>
       <c r="D90" t="b">
         <v>0</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>sw_log, sw</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>patterns_mat</t>
+          <t>intervals</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>opr</t>
+          <t>kh_md_ft</t>
         </is>
       </c>
       <c r="D91" t="b">
         <v>0</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>mD.ft</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>kh</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>patterns_mat</t>
+          <t>intervals</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>wpr</t>
+          <t>area_ac</t>
         </is>
       </c>
       <c r="D92" t="b">
         <v>0</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>acre</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>area, voronoi_area</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>injsand_calc</t>
+          <t>intervals</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>ooip_stb</t>
         </is>
       </c>
       <c r="D93" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>stb</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>ooip, stoiip, poes</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>injsand_calc</t>
+          <t>intervals</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>sand</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="D94" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>recovery_factor, fr</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>injsand_calc</t>
+          <t>intervals</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>eur_stb</t>
         </is>
       </c>
       <c r="D95" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>stb</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>eur</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>injsand_calc</t>
+          <t>intervals</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>tp</t>
+          <t>np_well_stb</t>
         </is>
       </c>
       <c r="D96" t="b">
         <v>0</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>stb</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>np_total_pozo_stb, np_total_pozo, np_well</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>intervals</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>np_ooip</t>
+        </is>
+      </c>
+      <c r="D97" t="b">
+        <v>0</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>np_ooip_ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>intervals</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>sw_act</t>
+        </is>
+      </c>
+      <c r="D98" t="b">
+        <v>0</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>sw_actual, sw_current</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>intervals</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>bsw0_pct</t>
+        </is>
+      </c>
+      <c r="D99" t="b">
+        <v>0</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>bsw_inicial_pct, bsw_inicial, bsw</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>intervals</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>qo0</t>
+        </is>
+      </c>
+      <c r="D100" t="b">
+        <v>0</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>bopd</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>qo_inicial_bopd, qo_inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>intervals</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>qw0</t>
+        </is>
+      </c>
+      <c r="D101" t="b">
+        <v>0</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>bwpd</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>qw_inicial_bwpd, qw_inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>intervals</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>qf0</t>
+        </is>
+      </c>
+      <c r="D102" t="b">
+        <v>0</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>bfpd</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>qf_inicial_bfpd, qf_inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>intervals</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>qa</t>
+        </is>
+      </c>
+      <c r="D103" t="b">
+        <v>0</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>qa_resultado, qa_result</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>profiles</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>orgunit</t>
+        </is>
+      </c>
+      <c r="D104" t="b">
+        <v>0</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>org_unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>profiles</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D105" t="b">
+        <v>0</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>profiles</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="D106" t="b">
+        <v>1</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>pozo</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>profiles</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>sand</t>
+        </is>
+      </c>
+      <c r="D107" t="b">
+        <v>0</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>unit, unidad, arena</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>profiles</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>interval_id</t>
+        </is>
+      </c>
+      <c r="D108" t="b">
+        <v>0</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>intervalo_id, intervalo, interval</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>profiles</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="D109" t="b">
+        <v>1</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>escenario, case</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>profiles</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D110" t="b">
+        <v>1</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>mes, t</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>profiles</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>qoi</t>
+        </is>
+      </c>
+      <c r="D111" t="b">
+        <v>0</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>bopd</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>qoi_bopd</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>profiles</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>qw0</t>
+        </is>
+      </c>
+      <c r="D112" t="b">
+        <v>0</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>bwpd</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>qwi_bwpd, qwi</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>profiles</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>qo</t>
+        </is>
+      </c>
+      <c r="D113" t="b">
+        <v>0</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>bopd</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>qo_perfil_bopd, qo_perfil</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>profiles</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>qw</t>
+        </is>
+      </c>
+      <c r="D114" t="b">
+        <v>0</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>bwpd</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>qw_perfil_bwpd, qw_perfil</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>profiles</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>qf</t>
+        </is>
+      </c>
+      <c r="D115" t="b">
+        <v>0</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>bfpd</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>qf_perfil_bfpd, qf_perfil</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>profiles</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D116" t="b">
+        <v>0</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>b_exp, b_hyp</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>profiles</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>di</t>
+        </is>
+      </c>
+      <c r="D117" t="b">
+        <v>0</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>1/month</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>di_por_mes, di_month</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>findings</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D118" t="b">
+        <v>1</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>fuente, analysis, analisis, study</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>findings</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="D119" t="b">
+        <v>1</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>pozo</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>findings</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>sand</t>
+        </is>
+      </c>
+      <c r="D120" t="b">
+        <v>0</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>unit, unidad, arena</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>findings</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>interval_id</t>
+        </is>
+      </c>
+      <c r="D121" t="b">
+        <v>0</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>intervalo_id, intervalo, interval</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>findings</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D122" t="b">
+        <v>1</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>accion, intervention, job, type</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>findings</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="D123" t="b">
+        <v>0</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>familia, evidence_family</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>findings</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="D124" t="b">
+        <v>0</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>variable, metrica</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>findings</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D125" t="b">
+        <v>0</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>findings</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D126" t="b">
+        <v>0</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>referencia, threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>findings</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>unit_label</t>
+        </is>
+      </c>
+      <c r="D127" t="b">
+        <v>0</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>units, unidades, uom</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>findings</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="D128" t="b">
+        <v>0</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>comentario, text, note</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>findings</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>gain_bopd</t>
+        </is>
+      </c>
+      <c r="D129" t="b">
+        <v>0</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>bopd</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>gain, qo_gain, incremental_bopd</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>findings</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D130" t="b">
+        <v>0</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>fecha, as_of</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>patterns</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D131" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>patterns</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D132" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>patterns</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>bopd</t>
+        </is>
+      </c>
+      <c r="D133" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>patterns</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>bwpd</t>
+        </is>
+      </c>
+      <c r="D134" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>patterns</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>bwipd</t>
+        </is>
+      </c>
+      <c r="D135" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>patterns_vel</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D136" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>patterns_vel</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D137" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>patterns_vel</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>wor</t>
+        </is>
+      </c>
+      <c r="D138" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>patterns_vel</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>util</t>
+        </is>
+      </c>
+      <c r="D139" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>patterns_vel</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="D140" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>patterns_vel</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>iwr</t>
+        </is>
+      </c>
+      <c r="D141" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D142" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D143" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>np</t>
+        </is>
+      </c>
+      <c r="D144" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>nw</t>
+        </is>
+      </c>
+      <c r="D145" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>nwi</t>
+        </is>
+      </c>
+      <c r="D146" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>iwrcum</t>
+        </is>
+      </c>
+      <c r="D147" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>opr</t>
+        </is>
+      </c>
+      <c r="D148" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>wpr</t>
+        </is>
+      </c>
+      <c r="D149" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
           <t>injsand_calc</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>derived</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D150" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>injsand_calc</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>sand</t>
+        </is>
+      </c>
+      <c r="D151" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>injsand_calc</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D152" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>injsand_calc</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="D153" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>injsand_calc</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
         <is>
           <t>nwi</t>
         </is>
       </c>
-      <c r="D97" t="b">
+      <c r="D154" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2942,33 +4495,133 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>orgunit</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>field</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>bopd</t>
+          <t>well</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>bwpd</t>
+          <t>sand</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>bwipd</t>
+          <t>interval_id</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>top_ft</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>base_ft</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>estado</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>h_net_ft</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>kabs_md</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>phi</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>sw_las</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>kh_md_ft</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>area_ac</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ooip_stb</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>eur_stb</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>np_well_stb</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>np_ooip</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sw_act</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>bsw0_pct</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>qo0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>qw0</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>qf0</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>qa</t>
         </is>
       </c>
     </row>
@@ -2979,38 +4632,78 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>orgunit</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>field</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>wor</t>
+          <t>well</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>util</t>
+          <t>sand</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>tp</t>
+          <t>interval_id</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>iwr</t>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>qoi</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>qw0</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>qo</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>qw</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>qf</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>di</t>
         </is>
       </c>
     </row>
@@ -3021,48 +4714,73 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>source</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sand</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>interval_id</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>unit_label</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>gain_bopd</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>np</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>nw</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>nwi</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>iwrcum</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>opr</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>wpr</t>
         </is>
       </c>
     </row>
@@ -3084,22 +4802,116 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>sand</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>bopd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>bwpd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>bwipd</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>date</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>wor</t>
+        </is>
+      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>util</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>tp</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>iwr</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>np</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nw</t>
+        </is>
+      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>nwi</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>iwrcum</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>opr</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>wpr</t>
         </is>
       </c>
     </row>
@@ -3145,6 +4957,43 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sand</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>nwi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D1"/>
@@ -3382,41 +5231,61 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>orgunit</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>field</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>substructure</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pattern</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>well</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>well_type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>y</t>
         </is>
@@ -3429,7 +5298,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3448,6 +5317,11 @@
           <t>np_primary</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/wf_template.xlsx
+++ b/data/wf_template.xlsx
@@ -23,10 +23,16 @@
     <sheet name="intervals" sheetId="14" r:id="rId14"/>
     <sheet name="profiles" sheetId="15" r:id="rId15"/>
     <sheet name="findings" sheetId="16" r:id="rId16"/>
-    <sheet name="patterns" sheetId="17" r:id="rId17"/>
-    <sheet name="patterns_vel" sheetId="18" r:id="rId18"/>
-    <sheet name="patterns_mat" sheetId="19" r:id="rId19"/>
-    <sheet name="injsand_calc" sheetId="20" r:id="rId20"/>
+    <sheet name="log_intervals" sheetId="17" r:id="rId17"/>
+    <sheet name="completions" sheetId="18" r:id="rId18"/>
+    <sheet name="interval_rates" sheetId="19" r:id="rId19"/>
+    <sheet name="interval_potential" sheetId="20" r:id="rId20"/>
+    <sheet name="job_costs" sheetId="21" r:id="rId21"/>
+    <sheet name="lift_status" sheetId="22" r:id="rId22"/>
+    <sheet name="patterns" sheetId="23" r:id="rId23"/>
+    <sheet name="patterns_vel" sheetId="24" r:id="rId24"/>
+    <sheet name="patterns_mat" sheetId="25" r:id="rId25"/>
+    <sheet name="injsand_calc" sheetId="26" r:id="rId26"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -370,7 +376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:G193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3853,480 +3859,1540 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>patterns</t>
+          <t>log_intervals</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D131" t="b">
         <v>1</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>algoritmo, method, source</t>
+        </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>patterns</t>
+          <t>log_intervals</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>well</t>
         </is>
       </c>
       <c r="D132" t="b">
         <v>1</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>pozo</t>
+        </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>patterns</t>
+          <t>log_intervals</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>bopd</t>
+          <t>top_ft</t>
         </is>
       </c>
       <c r="D133" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>top, tope</t>
+        </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>patterns</t>
+          <t>log_intervals</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>bwpd</t>
+          <t>base_ft</t>
         </is>
       </c>
       <c r="D134" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>base, bottom</t>
+        </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>patterns</t>
+          <t>log_intervals</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>bwipd</t>
+          <t>sand</t>
         </is>
       </c>
       <c r="D135" t="b">
         <v>0</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>unit, unidad, arena</t>
+        </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>patterns_vel</t>
+          <t>log_intervals</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>score</t>
         </is>
       </c>
       <c r="D136" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>confidence, probabilidad, quality</t>
+        </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>patterns_vel</t>
+          <t>completions</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>well</t>
         </is>
       </c>
       <c r="D137" t="b">
         <v>1</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>pozo</t>
+        </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>patterns_vel</t>
+          <t>completions</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>wor</t>
+          <t>top_ft</t>
         </is>
       </c>
       <c r="D138" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>top, tope</t>
+        </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>patterns_vel</t>
+          <t>completions</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>util</t>
+          <t>base_ft</t>
         </is>
       </c>
       <c r="D139" t="b">
         <v>0</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>base, bottom</t>
+        </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>patterns_vel</t>
+          <t>completions</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>tp</t>
+          <t>type</t>
         </is>
       </c>
       <c r="D140" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>tipo, completion_type, event</t>
+        </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>patterns_vel</t>
+          <t>completions</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>iwr</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D141" t="b">
         <v>0</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>patterns_mat</t>
+          <t>completions</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D142" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>estado</t>
+        </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>patterns_mat</t>
+          <t>completions</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>sand</t>
         </is>
       </c>
       <c r="D143" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>unit, unidad, arena</t>
+        </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>patterns_mat</t>
+          <t>interval_rates</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>well</t>
         </is>
       </c>
       <c r="D144" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>pozo</t>
+        </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>patterns_mat</t>
+          <t>interval_rates</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>nw</t>
+          <t>interval_id</t>
         </is>
       </c>
       <c r="D145" t="b">
         <v>0</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>intervalo_id, intervalo</t>
+        </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>patterns_mat</t>
+          <t>interval_rates</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>nwi</t>
+          <t>top_ft</t>
         </is>
       </c>
       <c r="D146" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>top, tope</t>
+        </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>patterns_mat</t>
+          <t>interval_rates</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>iwrcum</t>
+          <t>base_ft</t>
         </is>
       </c>
       <c r="D147" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>base, bottom</t>
+        </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>patterns_mat</t>
+          <t>interval_rates</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>opr</t>
+          <t>sand</t>
         </is>
       </c>
       <c r="D148" t="b">
         <v>0</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>unit, unidad, arena</t>
+        </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>patterns_mat</t>
+          <t>interval_rates</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>wpr</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D149" t="b">
         <v>0</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>injsand_calc</t>
+          <t>interval_rates</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>qo</t>
         </is>
       </c>
       <c r="D150" t="b">
         <v>1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>bopd</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>qo_bopd, oil_rate, bopd</t>
+        </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>injsand_calc</t>
+          <t>interval_rates</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>sand</t>
+          <t>qw</t>
         </is>
       </c>
       <c r="D151" t="b">
         <v>1</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>bwpd</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>qw_bwpd, water_rate, bwpd</t>
+        </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>injsand_calc</t>
+          <t>interval_rates</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>method</t>
         </is>
       </c>
       <c r="D152" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>metodo, source</t>
+        </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>injsand_calc</t>
+          <t>interval_potential</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>tp</t>
+          <t>well</t>
         </is>
       </c>
       <c r="D153" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>pozo</t>
+        </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>interval_potential</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>interval_id</t>
+        </is>
+      </c>
+      <c r="D154" t="b">
+        <v>0</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>intervalo_id, intervalo</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>interval_potential</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>top_ft</t>
+        </is>
+      </c>
+      <c r="D155" t="b">
+        <v>1</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>top, tope</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>interval_potential</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>base_ft</t>
+        </is>
+      </c>
+      <c r="D156" t="b">
+        <v>1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>base, bottom</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>interval_potential</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>sand</t>
+        </is>
+      </c>
+      <c r="D157" t="b">
+        <v>0</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>unit, unidad, arena</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>interval_potential</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>qo_theo</t>
+        </is>
+      </c>
+      <c r="D158" t="b">
+        <v>1</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>bopd</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>qo_teorico, qo_potential, qo_pot</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>interval_potential</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>qw_theo</t>
+        </is>
+      </c>
+      <c r="D159" t="b">
+        <v>0</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>bwpd</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>qw_teorico, qw_potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>job_costs</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>job_type</t>
+        </is>
+      </c>
+      <c r="D160" t="b">
+        <v>1</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>type, tipo, item</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>job_costs</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>depth_min_ft</t>
+        </is>
+      </c>
+      <c r="D161" t="b">
+        <v>0</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>depth_from, prof_min</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>job_costs</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>depth_max_ft</t>
+        </is>
+      </c>
+      <c r="D162" t="b">
+        <v>0</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>depth_to, prof_max</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>job_costs</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>cost_usd</t>
+        </is>
+      </c>
+      <c r="D163" t="b">
+        <v>1</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>cost, costo, usd</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>lift_status</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="D164" t="b">
+        <v>1</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>pozo</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>lift_status</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>lift_type</t>
+        </is>
+      </c>
+      <c r="D165" t="b">
+        <v>0</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>als_type, tipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>lift_status</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>install_date</t>
+        </is>
+      </c>
+      <c r="D166" t="b">
+        <v>1</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>installed, fecha_instalacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>lift_status</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>expected_runlife_days</t>
+        </is>
+      </c>
+      <c r="D167" t="b">
+        <v>0</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>runlife, expected_runlife, vida_util_dias</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>lift_status</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>capacity_bfpd</t>
+        </is>
+      </c>
+      <c r="D168" t="b">
+        <v>0</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>bfpd</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>capacity, capacidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>lift_status</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>failures_12m</t>
+        </is>
+      </c>
+      <c r="D169" t="b">
+        <v>0</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>failures, fallas_12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>patterns</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D170" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>patterns</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D171" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>patterns</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>bopd</t>
+        </is>
+      </c>
+      <c r="D172" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>patterns</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>bwpd</t>
+        </is>
+      </c>
+      <c r="D173" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>patterns</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>bwipd</t>
+        </is>
+      </c>
+      <c r="D174" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>patterns_vel</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D175" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>patterns_vel</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D176" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>patterns_vel</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>wor</t>
+        </is>
+      </c>
+      <c r="D177" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>patterns_vel</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>util</t>
+        </is>
+      </c>
+      <c r="D178" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>patterns_vel</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="D179" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>patterns_vel</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>iwr</t>
+        </is>
+      </c>
+      <c r="D180" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D181" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D182" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>np</t>
+        </is>
+      </c>
+      <c r="D183" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>nw</t>
+        </is>
+      </c>
+      <c r="D184" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>nwi</t>
+        </is>
+      </c>
+      <c r="D185" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>iwrcum</t>
+        </is>
+      </c>
+      <c r="D186" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>opr</t>
+        </is>
+      </c>
+      <c r="D187" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>patterns_mat</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>wpr</t>
+        </is>
+      </c>
+      <c r="D188" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
           <t>injsand_calc</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B189" t="inlineStr">
         <is>
           <t>derived</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D189" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>injsand_calc</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>sand</t>
+        </is>
+      </c>
+      <c r="D190" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>injsand_calc</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D191" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>injsand_calc</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="D192" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>injsand_calc</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
         <is>
           <t>nwi</t>
         </is>
       </c>
-      <c r="D154" t="b">
+      <c r="D193" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4791,33 +5857,38 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>well</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>bopd</t>
+          <t>top_ft</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>bwpd</t>
+          <t>base_ft</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>bwipd</t>
+          <t>sand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>score</t>
         </is>
       </c>
     </row>
@@ -4828,38 +5899,43 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>well</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>top_ft</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>base_ft</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>wor</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>util</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tp</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>iwr</t>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>sand</t>
         </is>
       </c>
     </row>
@@ -4870,48 +5946,53 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>well</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>interval_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>top_ft</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>base_ft</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>sand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>np</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>nw</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>nwi</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>iwrcum</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>opr</t>
+          <t>qo</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>wpr</t>
+          <t>qw</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>method</t>
         </is>
       </c>
     </row>
@@ -4959,6 +6040,258 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>interval_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>top_ft</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>base_ft</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>sand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>qo_theo</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>qw_theo</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>job_type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>depth_min_ft</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>depth_max_ft</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>cost_usd</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>lift_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>install_date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>expected_runlife_days</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity_bfpd</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>failures_12m</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>bopd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>bwpd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>bwipd</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>wor</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>util</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>iwr</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>np</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nw</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>nwi</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>iwrcum</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>opr</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>wpr</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
